--- a/bw_amr_ig/ValueSet-botswana-amr-specimen-site-vs.xlsx
+++ b/bw_amr_ig/ValueSet-botswana-amr-specimen-site-vs.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-09T10:14:37-04:00</t>
+    <t>2026-03-13T15:05:11-04:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/bw_amr_ig/ValueSet-botswana-amr-specimen-site-vs.xlsx
+++ b/bw_amr_ig/ValueSet-botswana-amr-specimen-site-vs.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-13T15:05:11-04:00</t>
+    <t>2026-03-13T15:54:56-04:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/bw_amr_ig/ValueSet-botswana-amr-specimen-site-vs.xlsx
+++ b/bw_amr_ig/ValueSet-botswana-amr-specimen-site-vs.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://bw.health.gov/fhir/ImplementationGuide/bw-amr-ig/ValueSet/botswana-amr-specimen-site-vs</t>
+    <t>http://bw.health.gov/fhir/amr/ValueSet/botswana-amr-specimen-site-vs</t>
   </si>
   <si>
     <t>Version</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-13T15:54:56-04:00</t>
+    <t>2026-03-13T21:27:21-04:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -135,7 +135,7 @@
     <t>Stool specimen</t>
   </si>
   <si>
-    <t>258603006</t>
+    <t>321667001</t>
   </si>
   <si>
     <t>Respiratory tract structure</t>
@@ -183,7 +183,7 @@
     <t>Catheter tip</t>
   </si>
   <si>
-    <t>302562005</t>
+    <t>119376003</t>
   </si>
   <si>
     <t>Tissue specimen</t>
